--- a/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_UserRole.xlsx
+++ b/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_UserRole.xlsx
@@ -885,7 +885,7 @@
   <sheetPr>
     <tabColor rgb="FFFFC000"/>
   </sheetPr>
-  <dimension ref="B1:E85"/>
+  <dimension ref="B1:G85"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.85546875" style="1" customWidth="1"/>
@@ -896,8 +896,8 @@
     <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:5" ht="25.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="2:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:7" ht="25.5" x14ac:dyDescent="0.2">
       <c r="B2" s="6" t="s">
         <v>43</v>
       </c>
@@ -908,14 +908,14 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:7" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="7"/>
       <c r="D3" s="10">
         <v>95000000000000</v>
       </c>
       <c r="E3" s="11"/>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B4" s="4" t="s">
         <v>0</v>
       </c>
@@ -927,8 +927,24 @@
         <f>IF(EXACT(B4, ""), "", CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_UserRole_SET""(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, ", (IF(EXACT(B4, ""), "NULL", CONCATENATE("'", B4, "'"))),"::varchar);"))</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Super User'::varchar);</v>
       </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G4" s="1" t="str">
+        <f>IF(EXACT($E4, ""), "", CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'name', ", IF(EXACT($B4, ""), "null", CONCATENATE("'", SUBSTITUTE($B4, "'", "\'"), "'")), "::varchar",
+")))::varchar;"))</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Super User'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="4" t="s">
         <v>1</v>
       </c>
@@ -940,1003 +956,1347 @@
         <f t="shared" ref="E5:E71" si="0">IF(EXACT(B5, ""), "", CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_UserRole_SET""(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, ", (IF(EXACT(B5, ""), "NULL", CONCATENATE("'", B5, "'"))),"::varchar);"))</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Guest'::varchar);</v>
       </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G5" s="1" t="str">
+        <f t="shared" ref="G5:G68" si="1">IF(EXACT($E5, ""), "", CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'name', ", IF(EXACT($B5, ""), "null", CONCATENATE("'", SUBSTITUTE($B5, "'", "\'"), "'")), "::varchar",
+")))::varchar;"))</f>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Guest'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B6" s="4"/>
       <c r="D6" s="13">
-        <f t="shared" ref="D6:D69" si="1" xml:space="preserve"> D5 + IF(EXACT(E6, ""), 0, 1)</f>
+        <f t="shared" ref="D6:D69" si="2" xml:space="preserve"> D5 + IF(EXACT(E6, ""), 0, 1)</f>
         <v>95000000000002</v>
       </c>
       <c r="E6" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G6" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B7" s="4" t="s">
         <v>65</v>
       </c>
       <c r="D7" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000003</v>
       </c>
       <c r="E7" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Default Employee Role'::varchar);</v>
       </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G7" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Default Employee Role'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B8" s="4"/>
       <c r="D8" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000003</v>
       </c>
       <c r="E8" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G8" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B9" s="4" t="s">
         <v>2</v>
       </c>
       <c r="D9" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000004</v>
       </c>
       <c r="E9" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Share Holder'::varchar);</v>
       </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G9" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Share Holder'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B10" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000005</v>
       </c>
       <c r="E10" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Stack Holder'::varchar);</v>
       </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G10" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Stack Holder'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B11" s="4" t="s">
         <v>4</v>
       </c>
       <c r="D11" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000006</v>
       </c>
       <c r="E11" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Public Accounting Firm'::varchar);</v>
       </c>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G11" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Public Accounting Firm'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B12" s="4" t="s">
         <v>6</v>
       </c>
       <c r="D12" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000007</v>
       </c>
       <c r="E12" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Commissary'::varchar);</v>
       </c>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G12" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Commissary'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B13" s="4"/>
       <c r="D13" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000007</v>
       </c>
       <c r="E13" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G13" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B14" s="4" t="s">
         <v>5</v>
       </c>
       <c r="D14" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000008</v>
       </c>
       <c r="E14" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Director'::varchar);</v>
       </c>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G14" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Director'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B15" s="4" t="s">
         <v>7</v>
       </c>
       <c r="D15" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000009</v>
       </c>
       <c r="E15" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'President Director'::varchar);</v>
       </c>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G15" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'President Director'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B16" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000010</v>
       </c>
       <c r="E16" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Finance Director'::varchar);</v>
       </c>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G16" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Finance Director'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D17" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000011</v>
       </c>
       <c r="E17" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Operational Director'::varchar);</v>
       </c>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G17" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Operational Director'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B18" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D18" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000012</v>
       </c>
       <c r="E18" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Marketing Director'::varchar);</v>
       </c>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G18" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Marketing Director'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B19" s="4" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000013</v>
       </c>
       <c r="E19" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Information Technology Director'::varchar);</v>
       </c>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G19" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Information Technology Director'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B20" s="4"/>
       <c r="D20" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000013</v>
       </c>
       <c r="E20" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G20" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B21" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D21" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000014</v>
       </c>
       <c r="E21" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Project General Manager'::varchar);</v>
       </c>
-    </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G21" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Project General Manager'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B22" s="4" t="s">
         <v>24</v>
       </c>
       <c r="D22" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000015</v>
       </c>
       <c r="E22" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Project Management Officer'::varchar);</v>
       </c>
-    </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G22" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Project Management Officer'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D23" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000016</v>
       </c>
       <c r="E23" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Finance, Accounting, &amp; Tax General Manager'::varchar);</v>
       </c>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G23" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Finance, Accounting, &amp; Tax General Manager'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B24" s="4" t="s">
         <v>13</v>
       </c>
       <c r="D24" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000017</v>
       </c>
       <c r="E24" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'HR, GA, &amp; TAM General Manager'::varchar);</v>
       </c>
-    </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G24" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'HR, GA, &amp; TAM General Manager'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B25" s="4" t="s">
         <v>14</v>
       </c>
       <c r="D25" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000018</v>
       </c>
       <c r="E25" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Sales General Manager'::varchar);</v>
       </c>
-    </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G25" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Sales General Manager'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B26" s="4"/>
       <c r="D26" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000018</v>
       </c>
       <c r="E26" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G26" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B27" s="4" t="s">
         <v>25</v>
       </c>
       <c r="D27" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000019</v>
       </c>
       <c r="E27" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Project Manager'::varchar);</v>
       </c>
-    </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G27" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Project Manager'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B28" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D28" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000020</v>
       </c>
       <c r="E28" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Site Manager'::varchar);</v>
       </c>
-    </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G28" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Site Manager'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B29" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D29" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000021</v>
       </c>
       <c r="E29" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Project Controller Coordinator'::varchar);</v>
       </c>
-    </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G29" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Project Controller Coordinator'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B30" s="4" t="s">
         <v>27</v>
       </c>
       <c r="D30" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000022</v>
       </c>
       <c r="E30" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Project Controller Staff'::varchar);</v>
       </c>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G30" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Project Controller Staff'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B31" s="4" t="s">
         <v>63</v>
       </c>
       <c r="D31" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000023</v>
       </c>
       <c r="E31" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Project Administrator Coordinator'::varchar);</v>
       </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G31" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Project Administrator Coordinator'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B32" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D32" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000024</v>
       </c>
       <c r="E32" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Project Administrator Staff'::varchar);</v>
       </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G32" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Project Administrator Staff'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B33" s="4" t="s">
         <v>62</v>
       </c>
       <c r="D33" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000025</v>
       </c>
       <c r="E33" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Project Worker Coordinator'::varchar);</v>
       </c>
-    </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G33" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Project Worker Coordinator'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="34" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B34" s="4" t="s">
         <v>29</v>
       </c>
       <c r="D34" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000026</v>
       </c>
       <c r="E34" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Project Worker Staff'::varchar);</v>
       </c>
-    </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G34" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Project Worker Staff'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="35" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B35" s="4"/>
       <c r="D35" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000026</v>
       </c>
       <c r="E35" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G35" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B36" s="4" t="s">
         <v>15</v>
       </c>
       <c r="D36" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000027</v>
       </c>
       <c r="E36" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Finance Manager'::varchar);</v>
       </c>
-    </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G36" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Finance Manager'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="37" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B37" s="4" t="s">
         <v>60</v>
       </c>
       <c r="D37" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000028</v>
       </c>
       <c r="E37" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Cashier &amp; Treasury Coordinator'::varchar);</v>
       </c>
-    </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G37" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Cashier &amp; Treasury Coordinator'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="38" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B38" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D38" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000029</v>
       </c>
       <c r="E38" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Cashier &amp; Treasury Staff'::varchar);</v>
       </c>
-    </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G38" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Cashier &amp; Treasury Staff'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="39" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B39" s="4" t="s">
         <v>61</v>
       </c>
       <c r="D39" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000030</v>
       </c>
       <c r="E39" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Cost Controller Coordinator'::varchar);</v>
       </c>
-    </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G39" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Cost Controller Coordinator'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="40" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B40" s="4" t="s">
         <v>17</v>
       </c>
       <c r="D40" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000031</v>
       </c>
       <c r="E40" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Cost Controller Staff'::varchar);</v>
       </c>
-    </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G40" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Cost Controller Staff'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="41" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B41" s="4"/>
       <c r="D41" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000031</v>
       </c>
       <c r="E41" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="42" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G41" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B42" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D42" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000032</v>
       </c>
       <c r="E42" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Accounting &amp; Tax Manager'::varchar);</v>
       </c>
-    </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G42" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Accounting &amp; Tax Manager'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="43" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B43" s="4" t="s">
         <v>59</v>
       </c>
       <c r="D43" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000033</v>
       </c>
       <c r="E43" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Accounting &amp; Tax Coordinator'::varchar);</v>
       </c>
-    </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G43" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Accounting &amp; Tax Coordinator'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="44" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B44" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D44" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000034</v>
       </c>
       <c r="E44" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Accounting &amp; Tax Staff'::varchar);</v>
       </c>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G44" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Accounting &amp; Tax Staff'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="45" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B45" s="4"/>
       <c r="D45" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000034</v>
       </c>
       <c r="E45" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G45" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B46" s="4" t="s">
         <v>20</v>
       </c>
       <c r="D46" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000035</v>
       </c>
       <c r="E46" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'IT System Manager'::varchar);</v>
       </c>
-    </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G46" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'IT System Manager'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="47" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B47" s="4" t="s">
         <v>48</v>
       </c>
       <c r="D47" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000036</v>
       </c>
       <c r="E47" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'IT System Engineer Coordinator'::varchar);</v>
       </c>
-    </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G47" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'IT System Engineer Coordinator'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="48" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B48" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D48" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000037</v>
       </c>
       <c r="E48" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'IT System Engineer Staff'::varchar);</v>
       </c>
-    </row>
-    <row r="49" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G48" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'IT System Engineer Staff'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B49" s="4" t="s">
         <v>49</v>
       </c>
       <c r="D49" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000038</v>
       </c>
       <c r="E49" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'IT Software Engineer Coordinator'::varchar);</v>
       </c>
-    </row>
-    <row r="50" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G49" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'IT Software Engineer Coordinator'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="50" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B50" s="4" t="s">
         <v>22</v>
       </c>
       <c r="D50" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000039</v>
       </c>
       <c r="E50" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'IT Software Engineer Staff'::varchar);</v>
       </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G50" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'IT Software Engineer Staff'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B51" s="4"/>
       <c r="D51" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000039</v>
       </c>
       <c r="E51" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G51" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B52" s="4" t="s">
         <v>30</v>
       </c>
       <c r="D52" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000040</v>
       </c>
       <c r="E52" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Procurement Manager'::varchar);</v>
       </c>
-    </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G52" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Procurement Manager'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="53" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B53" s="4" t="s">
         <v>50</v>
       </c>
       <c r="D53" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000041</v>
       </c>
       <c r="E53" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Procurement Coordinator'::varchar);</v>
       </c>
-    </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G53" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Procurement Coordinator'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="54" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B54" s="4" t="s">
         <v>31</v>
       </c>
       <c r="D54" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000042</v>
       </c>
       <c r="E54" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Procurement Staff'::varchar);</v>
       </c>
-    </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G54" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Procurement Staff'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="55" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B55" s="4"/>
       <c r="D55" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000042</v>
       </c>
       <c r="E55" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G55" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B56" s="4" t="s">
         <v>32</v>
       </c>
       <c r="D56" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000043</v>
       </c>
       <c r="E56" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Sales Manager'::varchar);</v>
       </c>
-    </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G56" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Sales Manager'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="57" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B57" s="4" t="s">
         <v>51</v>
       </c>
       <c r="D57" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000044</v>
       </c>
       <c r="E57" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Sales Coordinator'::varchar);</v>
       </c>
-    </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G57" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Sales Coordinator'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="58" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B58" s="4" t="s">
         <v>66</v>
       </c>
       <c r="D58" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000045</v>
       </c>
       <c r="E58" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Bid And Sales Administrator Staff'::varchar);</v>
       </c>
-    </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G58" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Bid And Sales Administrator Staff'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="59" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B59" s="4" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000046</v>
       </c>
       <c r="E59" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Sales Estimator Coordinator'::varchar);</v>
       </c>
-    </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G59" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Sales Estimator Coordinator'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="60" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B60" s="4" t="s">
         <v>67</v>
       </c>
       <c r="D60" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000047</v>
       </c>
       <c r="E60" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Sales Estimator Staff'::varchar);</v>
       </c>
-    </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G60" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Sales Estimator Staff'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="61" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B61" s="4"/>
       <c r="D61" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000047</v>
       </c>
       <c r="E61" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G61" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="62" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B62" s="4" t="s">
         <v>33</v>
       </c>
       <c r="D62" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000048</v>
       </c>
       <c r="E62" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Health Safety Environment Manager'::varchar);</v>
       </c>
-    </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G62" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Health Safety Environment Manager'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="63" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B63" s="4" t="s">
         <v>53</v>
       </c>
       <c r="D63" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000049</v>
       </c>
       <c r="E63" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Health Safety Environment Coordinator'::varchar);</v>
       </c>
-    </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G63" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Health Safety Environment Coordinator'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="64" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B64" s="4" t="s">
         <v>34</v>
       </c>
       <c r="D64" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000050</v>
       </c>
       <c r="E64" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Health Safety Environment Staff'::varchar);</v>
       </c>
-    </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G64" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Health Safety Environment Staff'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="65" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B65" s="4"/>
       <c r="D65" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000050</v>
       </c>
       <c r="E65" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G65" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="66" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B66" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D66" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000051</v>
       </c>
       <c r="E66" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Human Resource Development Manager'::varchar);</v>
       </c>
-    </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G66" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Human Resource Development Manager'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="67" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B67" s="4" t="s">
         <v>54</v>
       </c>
       <c r="D67" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000052</v>
       </c>
       <c r="E67" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Human Resource Development Coordinator'::varchar);</v>
       </c>
-    </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G67" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Human Resource Development Coordinator'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="68" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B68" s="4" t="s">
         <v>36</v>
       </c>
       <c r="D68" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000053</v>
       </c>
       <c r="E68" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Human Resource Development Staff'::varchar);</v>
       </c>
-    </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G68" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Human Resource Development Staff'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="69" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B69" s="4"/>
       <c r="D69" s="13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>95000000000053</v>
       </c>
       <c r="E69" s="12" t="str">
         <f t="shared" si="0"/>
         <v/>
       </c>
-    </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G69" s="1" t="str">
+        <f t="shared" ref="G69:G84" si="3">IF(EXACT($E69, ""), "", CONCATENATE(
+"varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT (",
+"'recordID', NULL::bigint,", "'entities', ", "JSON_BUILD_OBJECT (",
+"'sysLoginSession_RefID', varSystemLoginSession::bigint,",
+"'sysDataAnnotation', NULL::varchar,",
+"'sysDataSetDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityStartDateTimeTZ', NULL::timestamptz,",
+"'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,",
+"'sysPartitionRemovableRecordKey_RefID', NULL::bigint,",
+"'sysBranch_RefID', varInstitutionBranchID::bigint,",
+"'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,",
+"'name', ", IF(EXACT($B69, ""), "null", CONCATENATE("'", SUBSTITUTE($B69, "'", "\'"), "'")), "::varchar",
+")))::varchar;"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B70" s="4" t="s">
         <v>39</v>
       </c>
       <c r="D70" s="13">
-        <f t="shared" ref="D70:D84" si="2" xml:space="preserve"> D69 + IF(EXACT(E70, ""), 0, 1)</f>
+        <f t="shared" ref="D70:D84" si="4" xml:space="preserve"> D69 + IF(EXACT(E70, ""), 0, 1)</f>
         <v>95000000000054</v>
       </c>
       <c r="E70" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'General Affairs Manager'::varchar);</v>
       </c>
-    </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G70" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'General Affairs Manager'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="71" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B71" s="4" t="s">
         <v>55</v>
       </c>
       <c r="D71" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>95000000000055</v>
       </c>
       <c r="E71" s="12" t="str">
         <f t="shared" si="0"/>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'General Affairs Coordinator'::varchar);</v>
       </c>
-    </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G71" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'General Affairs Coordinator'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="72" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B72" s="4" t="s">
         <v>40</v>
       </c>
       <c r="D72" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>95000000000056</v>
       </c>
       <c r="E72" s="12" t="str">
-        <f t="shared" ref="E72:E84" si="3">IF(EXACT(B72, ""), "", CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_UserRole_SET""(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, ", (IF(EXACT(B72, ""), "NULL", CONCATENATE("'", B72, "'"))),"::varchar);"))</f>
+        <f t="shared" ref="E72:E84" si="5">IF(EXACT(B72, ""), "", CONCATENATE("PERFORM ""SchSysConfig"".""Func_TblAppObject_UserRole_SET""(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, ", (IF(EXACT(B72, ""), "NULL", CONCATENATE("'", B72, "'"))),"::varchar);"))</f>
         <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'General Affairs Staff'::varchar);</v>
       </c>
-    </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="G72" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'General Affairs Staff'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="73" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B73" s="4"/>
       <c r="D73" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>95000000000056</v>
       </c>
       <c r="E73" s="12" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G73" s="1" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B74" s="4" t="s">
         <v>41</v>
       </c>
       <c r="D74" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>95000000000057</v>
       </c>
       <c r="E74" s="12" t="str">
+        <f t="shared" si="5"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Legal Manager'::varchar);</v>
+      </c>
+      <c r="G74" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Legal Manager'::varchar);</v>
-      </c>
-    </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Legal Manager'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="75" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B75" s="4" t="s">
         <v>56</v>
       </c>
       <c r="D75" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>95000000000058</v>
       </c>
       <c r="E75" s="12" t="str">
+        <f t="shared" si="5"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Legal Coordinator'::varchar);</v>
+      </c>
+      <c r="G75" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Legal Coordinator'::varchar);</v>
-      </c>
-    </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Legal Coordinator'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="76" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B76" s="4" t="s">
         <v>42</v>
       </c>
       <c r="D76" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>95000000000059</v>
       </c>
       <c r="E76" s="12" t="str">
+        <f t="shared" si="5"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Legal Staff'::varchar);</v>
+      </c>
+      <c r="G76" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Legal Staff'::varchar);</v>
-      </c>
-    </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Legal Staff'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="77" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B77" s="4"/>
       <c r="D77" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>95000000000059</v>
       </c>
       <c r="E77" s="12" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G77" s="1" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B78" s="4" t="s">
         <v>37</v>
       </c>
       <c r="D78" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>95000000000060</v>
       </c>
       <c r="E78" s="12" t="str">
+        <f t="shared" si="5"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Tools And Asset Manager'::varchar);</v>
+      </c>
+      <c r="G78" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Tools And Asset Manager'::varchar);</v>
-      </c>
-    </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Tools And Asset Manager'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="79" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B79" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D79" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>95000000000061</v>
       </c>
       <c r="E79" s="12" t="str">
+        <f t="shared" si="5"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Tools And Asset Coordinator'::varchar);</v>
+      </c>
+      <c r="G79" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Tools And Asset Coordinator'::varchar);</v>
-      </c>
-    </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Tools And Asset Coordinator'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="80" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B80" s="4" t="s">
         <v>38</v>
       </c>
       <c r="D80" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>95000000000062</v>
       </c>
       <c r="E80" s="12" t="str">
+        <f t="shared" si="5"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Tools And Asset Staff'::varchar);</v>
+      </c>
+      <c r="G80" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Tools And Asset Staff'::varchar);</v>
-      </c>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Tools And Asset Staff'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="81" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B81" s="4"/>
       <c r="D81" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>95000000000062</v>
       </c>
       <c r="E81" s="12" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="G81" s="1" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="82" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B82" s="4" t="s">
         <v>46</v>
       </c>
       <c r="D82" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>95000000000063</v>
       </c>
       <c r="E82" s="12" t="str">
+        <f t="shared" si="5"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Engineering Manager'::varchar);</v>
+      </c>
+      <c r="G82" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Engineering Manager'::varchar);</v>
-      </c>
-    </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Engineering Manager'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="83" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B83" s="4" t="s">
         <v>58</v>
       </c>
       <c r="D83" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>95000000000064</v>
       </c>
       <c r="E83" s="12" t="str">
+        <f t="shared" si="5"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Engineering Coordinator'::varchar);</v>
+      </c>
+      <c r="G83" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Engineering Coordinator'::varchar);</v>
-      </c>
-    </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Engineering Coordinator'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="84" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B84" s="4" t="s">
         <v>47</v>
       </c>
       <c r="D84" s="13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>95000000000065</v>
       </c>
       <c r="E84" s="12" t="str">
+        <f t="shared" si="5"/>
+        <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Engineering Staff'::varchar);</v>
+      </c>
+      <c r="G84" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>PERFORM "SchSysConfig"."Func_TblAppObject_UserRole_SET"(varSystemLoginSession, null::bigint, null::varchar, null::timestamptz, null::timestamptz, null::varchar, varInstitutionBranchID, varBaseCurrencyID, 'Engineering Staff'::varchar);</v>
-      </c>
-    </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.2">
+        <v>varSQL := varSQL || (CASE WHEN (varSQL = '') THEN '' ELSE ', ' END) || (SELECT JSON_BUILD_OBJECT ('recordID', NULL::bigint,'entities', JSON_BUILD_OBJECT ('sysLoginSession_RefID', varSystemLoginSession::bigint,'sysDataAnnotation', NULL::varchar,'sysDataSetDateTimeTZ', NULL::timestamptz,'sysDataValidityStartDateTimeTZ', NULL::timestamptz,'sysDataValidityFinishDateTimeTZ', NULL::timestamptz,'sysPartitionRemovableRecordKey_RefID', NULL::bigint,'sysBranch_RefID', varInstitutionBranchID::bigint,'sysBaseCurrency_RefID',varBaseCurrencyID::bigint,'name', 'Engineering Staff'::varchar)))::varchar;</v>
+      </c>
+    </row>
+    <row r="85" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B85" s="5"/>
       <c r="D85" s="14"/>
       <c r="E85" s="15"/>

--- a/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_UserRole.xlsx
+++ b/Documentation/Documents/SQL Generator/Data Initial/SysConfig.TblAppObject_UserRole.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6585"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6585" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="MAIN" sheetId="1" r:id="rId1"/>
